--- a/Output Excel/lfsa_egan22d_raw.xlsx
+++ b/Output Excel/lfsa_egan22d_raw.xlsx
@@ -12247,7 +12247,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>1361.6</v>
+        <v>1361.7</v>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
@@ -38324,7 +38324,7 @@
         </is>
       </c>
       <c r="H475" t="n">
-        <v>159703.4</v>
+        <v>159703.5</v>
       </c>
       <c r="I475" t="inlineStr"/>
       <c r="J475" t="inlineStr">
@@ -41832,7 +41832,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>201627.4</v>
+        <v>201627.5</v>
       </c>
       <c r="I519" t="inlineStr"/>
       <c r="J519" t="inlineStr">
@@ -49725,7 +49725,7 @@
         </is>
       </c>
       <c r="H618" t="n">
-        <v>323</v>
+        <v>323.1</v>
       </c>
       <c r="I618" t="inlineStr"/>
       <c r="J618" t="inlineStr">
